--- a/artfynd/A 18215-2024 artfynd.xlsx
+++ b/artfynd/A 18215-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,74 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101389954</v>
+        <v>101870467</v>
       </c>
       <c r="B2" t="n">
-        <v>57150</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208260</v>
+        <v>221343</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Banvallen, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>605787.496592554</v>
+        <v>605920</v>
       </c>
       <c r="R2" t="n">
-        <v>6689313.408581567</v>
+        <v>6689358</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,27 +744,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-05-23</t>
+          <t>2022-06-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-05-23</t>
+          <t>2022-06-24</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>vilade i solen, begav sig iväg sen</t>
+          <t>Rikligt längs en sträcka på ca 20 meter av banvallen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,15 +780,262 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Johannes Lundberg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Johannes Lundberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>108889642</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Infart Ö Karinmossen, Österfärnebo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>605751</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6689833</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-05-08</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-05-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Simon Stenberg Jönsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Simon Stenberg Jönsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>101389954</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56905</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Banvallen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>605788</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6689313</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hedesunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-05-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-05-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>vilade i solen, begav sig iväg sen</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Manuela Scheuerer</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Manuela Scheuerer</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18215-2024 artfynd.xlsx
+++ b/artfynd/A 18215-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101870467</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108889642</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1036,8 +1051,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101389954</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>